--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.37149420282891</v>
+        <v>11.9228678079597</v>
       </c>
       <c r="D2" t="n">
-        <v>75.29384163317027</v>
+        <v>12.23524926539017</v>
       </c>
       <c r="E2" t="n">
-        <v>19.78822368189383</v>
+        <v>3.215586348307747</v>
       </c>
       <c r="F2" t="n">
-        <v>22.11290371382186</v>
+        <v>3.593346853496053</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.59904701933263</v>
+        <v>10.00984514064155</v>
       </c>
       <c r="D3" t="n">
-        <v>61.61383086106157</v>
+        <v>10.0122475149225</v>
       </c>
       <c r="E3" t="n">
-        <v>19.78822368189383</v>
+        <v>3.215586348307747</v>
       </c>
       <c r="F3" t="n">
-        <v>22.11290371382186</v>
+        <v>3.593346853496053</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>53.40305509737416</v>
+        <v>8.677996453323301</v>
       </c>
       <c r="D4" t="n">
-        <v>36.26020976320092</v>
+        <v>5.892284086520149</v>
       </c>
       <c r="E4" t="n">
-        <v>19.78822368189383</v>
+        <v>3.215586348307747</v>
       </c>
       <c r="F4" t="n">
-        <v>22.11290371382186</v>
+        <v>3.593346853496053</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.13295897392086</v>
+        <v>3.271605833262141</v>
       </c>
       <c r="D5" t="n">
-        <v>18.20220843001411</v>
+        <v>2.957858869877292</v>
       </c>
       <c r="E5" t="n">
-        <v>19.78822368189383</v>
+        <v>3.215586348307747</v>
       </c>
       <c r="F5" t="n">
-        <v>22.11290371382186</v>
+        <v>3.593346853496053</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
